--- a/samples/wy_vt_large.xlsx
+++ b/samples/wy_vt_large.xlsx
@@ -10,7 +10,9 @@
     <sheet name="Leads" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="QA Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$K$76</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -18,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,13 +28,27 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00217346"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDF3EF"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -47,8 +63,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -416,59 +434,72 @@
   </sheetPr>
   <dimension ref="A1:K76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="29" customWidth="1" min="11" max="11"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>DOT#</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Street</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ZIP</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Power units</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Drivers</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Cargo</t>
         </is>
@@ -522,47 +553,47 @@
       <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>40362</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>DFA NORTHEAST LOGISTICS INC</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>138 FEDERAL STREET</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>ST ALBANS</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>VT</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>05478</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="2" t="n">
         <v>133</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="2" t="n">
         <v>133</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="2" t="n">
         <v>186</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>MILK &amp; MILK PRODUCTS</t>
         </is>
@@ -612,51 +643,51 @@
       <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>86320</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>BELLAVANCE TRUCKING INC</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>(802) 479-9311</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>33 SMITH STREET</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>BARRE</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>VT</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>05641</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="2" t="n">
         <v>116</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" s="2" t="n">
         <v>116</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" s="2" t="n">
         <v>96</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>STONE</t>
         </is>
@@ -710,51 +741,51 @@
       <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>100348</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>BIG CO</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>(307) 864-3397</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>101 AMORETTI</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>THERMOPOLIS</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>WY</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>82443</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -808,47 +839,47 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>101191</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>RYAN BROS TRUCKING INC</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>180 LANE 3</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>THERMOPOLIS</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>WY</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>82443</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="2" t="n">
         <v>67</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="2" t="n">
         <v>67</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>ASPHALT</t>
         </is>
@@ -906,51 +937,51 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>106211</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>FARRELL DISTRIBUTING CORPORATION</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>(802) 864-4422</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>5 HOLMES RD</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>SO BURLINGTON</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>VT</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>05403</t>
         </is>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="2" t="n">
         <v>56</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" s="2" t="n">
         <v>56</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>PACKED CHIPS &amp; PRETZELS</t>
         </is>
@@ -1004,51 +1035,51 @@
       <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>155142</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>ADMIRAL TRANSPORT CORPORATION</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>(307) 278-2024</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>821 PULLIAM</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>WORLAND</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>WY</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>82401</t>
         </is>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" s="2" t="n">
         <v>519</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13" s="2" t="n">
         <v>516</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" s="2" t="n">
         <v>849</v>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1102,51 +1133,51 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>175899</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>HOMAX OIL SALES INC</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>(307) 237-5800</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>605 SOUTH POPLAR</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>CASPER</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>WY</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>82601</t>
         </is>
       </c>
-      <c r="H15" t="n">
+      <c r="H15" s="2" t="n">
         <v>97</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" s="2" t="n">
         <v>64</v>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1196,51 +1227,51 @@
       <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>198988</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>S D IRELAND CONCRETE CONSTRUCTION CORP</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>(802) 863-6222</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>193 INDUSTRIAL AVE</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>WILLISTON</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>VT</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>05495</t>
         </is>
       </c>
-      <c r="H17" t="n">
+      <c r="H17" s="2" t="n">
         <v>126</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17" s="2" t="n">
         <v>126</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17" s="2" t="n">
         <v>95</v>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1290,47 +1321,47 @@
       <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>224100</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>CASELLA WASTE MANAGEMENT INC</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr"/>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>25 GREENS HILL LANE</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>RUTLAND</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>VT</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>05701</t>
         </is>
       </c>
-      <c r="H19" t="n">
+      <c r="H19" s="2" t="n">
         <v>233</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I19" s="2" t="n">
         <v>233</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J19" s="2" t="n">
         <v>205</v>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>RECYCLABLES</t>
         </is>
@@ -1384,51 +1415,51 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>281308</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>JTL GROUP INC</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>(406) 651-2500</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>1461 BRYAN STOCK TRAIL</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>CASPER</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>WY</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>82601</t>
         </is>
       </c>
-      <c r="H21" t="n">
+      <c r="H21" s="2" t="n">
         <v>97</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21" s="2" t="n">
         <v>91</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J21" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>ASPHALT AND CONCRETE</t>
         </is>
@@ -1486,51 +1517,51 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>316634</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>D R M INC</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>(307) 682-0328</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>135 NORTHERN DRIVE</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>GILLETTE</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>WY</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>82716</t>
         </is>
       </c>
-      <c r="H23" t="n">
+      <c r="H23" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I23" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J23" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>SAND AND GRAVEL</t>
         </is>
@@ -1584,51 +1615,51 @@
       <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>351303</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>R K MILES INC</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>(802) 362-1952</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>618 DEPOT ST</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>MANCHESTER CENTER</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>VT</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>05255</t>
         </is>
       </c>
-      <c r="H25" t="n">
+      <c r="H25" s="2" t="n">
         <v>84</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I25" s="2" t="n">
         <v>82</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J25" s="2" t="n">
         <v>61</v>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1682,47 +1713,47 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>365122</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>LAMOILLE VALLEY TRANSPORTATION INC</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr"/>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>643  VT RT 15 W</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>MORRISVILLE</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>VT</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>05661-9736</t>
         </is>
       </c>
-      <c r="H27" t="n">
+      <c r="H27" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J27" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1772,51 +1803,51 @@
       <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>381386</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>TETON DISTRIBUTORS INC</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>(307) 278-2776</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>821 PULLIAM</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>WORLAND</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>WY</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>82401</t>
         </is>
       </c>
-      <c r="H29" t="n">
+      <c r="H29" s="2" t="n">
         <v>86</v>
       </c>
-      <c r="I29" t="n">
+      <c r="I29" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J29" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1862,51 +1893,51 @@
       <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>430976</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>MOSER ENGINE SERVICE</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>(307) 234-7833</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>260 CRAIG THOMAS BLVD</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>EVANSVILLE</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>WY</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>82636</t>
         </is>
       </c>
-      <c r="H31" t="n">
+      <c r="H31" s="2" t="n">
         <v>77</v>
       </c>
-      <c r="I31" t="n">
+      <c r="I31" s="2" t="n">
         <v>77</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J31" s="2" t="n">
         <v>67</v>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>SERVICE EQUIPMENT</t>
         </is>
@@ -1964,51 +1995,51 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>442045</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>GRAND AVENUE ENTERPRISES INC</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>(802) 868-2761</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>126 GRAND AVENUE</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>SWANTON</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>VT</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>05488</t>
         </is>
       </c>
-      <c r="H33" t="n">
+      <c r="H33" s="2" t="n">
         <v>89</v>
       </c>
-      <c r="I33" t="n">
+      <c r="I33" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J33" t="n">
+      <c r="J33" s="2" t="n">
         <v>81</v>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2054,51 +2085,51 @@
       <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>472791</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>CASELLA CONSTRUCTION INC</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>(802) 773-0052</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>1385 US ROUTE 7</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>PITTSFORD</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>VT</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>05763</t>
         </is>
       </c>
-      <c r="H35" t="n">
+      <c r="H35" s="2" t="n">
         <v>89</v>
       </c>
-      <c r="I35" t="n">
+      <c r="I35" s="2" t="n">
         <v>89</v>
       </c>
-      <c r="J35" t="n">
+      <c r="J35" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2148,51 +2179,51 @@
       <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>476802</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>NUCOR INC</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>(307) 856-1577</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>4424 SKYLANE AVE</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>RIVERTON</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>WY</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>82501</t>
         </is>
       </c>
-      <c r="H37" t="n">
+      <c r="H37" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="I37" t="n">
+      <c r="I37" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="J37" t="n">
+      <c r="J37" s="2" t="n">
         <v>74</v>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2242,51 +2273,51 @@
       <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>490436</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>PREMIER COACH CO INC</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>(802) 655-4456</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>946 ROUTE 7 SOUTH</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>MILTON</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>VT</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>05468</t>
         </is>
       </c>
-      <c r="H39" t="n">
+      <c r="H39" s="2" t="n">
         <v>91</v>
       </c>
-      <c r="I39" t="n">
+      <c r="I39" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J39" t="n">
+      <c r="J39" s="2" t="n">
         <v>121</v>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2336,51 +2367,51 @@
       <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>536800</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>ALBANY COUNTY SCHOOL DISTRICT ONE</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>(307) 721-4400</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>1948 E GRAND AVE</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>LARAMIE</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>WY</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>82070-4317</t>
         </is>
       </c>
-      <c r="H41" t="n">
+      <c r="H41" s="2" t="n">
         <v>64</v>
       </c>
-      <c r="I41" t="n">
+      <c r="I41" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J41" t="n">
+      <c r="J41" s="2" t="n">
         <v>84</v>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2430,51 +2461,51 @@
       <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>692712</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>TCRI ENERGY SERVICES INC</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>(307) 682-2706</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>1106 E LINCOLN STREET</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>GILLETTE</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>WY</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>82716</t>
         </is>
       </c>
-      <c r="H43" t="n">
+      <c r="H43" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="I43" t="n">
+      <c r="I43" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="J43" t="n">
+      <c r="J43" s="2" t="n">
         <v>89</v>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="K43" s="2" t="inlineStr">
         <is>
           <t>WATER HAULING</t>
         </is>
@@ -2528,51 +2559,51 @@
       <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>863077</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>SCHULTE TA INC</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>(307) 685-3181</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>5950 SWANSON RD</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>GILLETTE</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>WY</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>82718</t>
         </is>
       </c>
-      <c r="H45" t="n">
+      <c r="H45" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="I45" t="n">
+      <c r="I45" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="J45" t="n">
+      <c r="J45" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2618,51 +2649,51 @@
       <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>1026626</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>COMPRESSION LEASING SERVICES INC</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>(307) 265-3242</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>1935 NORTH LOOP ROAD</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>CASPER</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>WY</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>82601</t>
         </is>
       </c>
-      <c r="H47" t="n">
+      <c r="H47" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="I47" t="n">
+      <c r="I47" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="J47" t="n">
+      <c r="J47" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2712,51 +2743,51 @@
       <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>1145420</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>SOUTHEAST VERMONT TRANSIT INC</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>(802) 464-8487</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>45 MILL STREET</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>WILMINGTON</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>VT</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>05363</t>
         </is>
       </c>
-      <c r="H49" t="n">
+      <c r="H49" s="2" t="n">
         <v>67</v>
       </c>
-      <c r="I49" t="n">
+      <c r="I49" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J49" t="n">
+      <c r="J49" s="2" t="n">
         <v>70</v>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2810,51 +2841,51 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>1223293</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>WYOMING ENVIRONMENTAL SERVICES</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>(800) 479-9173</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>1754 INTERCHANGE RD</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>ROCK SPRINGS</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>WY</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>82901</t>
         </is>
       </c>
-      <c r="H51" t="n">
+      <c r="H51" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="I51" t="n">
+      <c r="I51" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="J51" t="n">
+      <c r="J51" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="K51" s="2" t="inlineStr">
         <is>
           <t>TRASH</t>
         </is>
@@ -2908,51 +2939,51 @@
       <c r="K52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>1255632</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>GREEN MOUNTAIN POWER CORPORATION</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>(888) 835-4672</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>163 ACORN LANE</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>COLCHESTER</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>VT</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>05446</t>
         </is>
       </c>
-      <c r="H53" t="n">
+      <c r="H53" s="2" t="n">
         <v>174</v>
       </c>
-      <c r="I53" t="n">
+      <c r="I53" s="2" t="n">
         <v>173</v>
       </c>
-      <c r="J53" t="n">
+      <c r="J53" s="2" t="n">
         <v>235</v>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="K53" s="2" t="inlineStr">
         <is>
           <t>ELECTRICAL</t>
         </is>
@@ -3006,51 +3037,51 @@
       <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>1415274</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>REDI SERVICES LLC</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>(307) 787-6333</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>225 W OWEN ST</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>LYMAN</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>WY</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>82937</t>
         </is>
       </c>
-      <c r="H55" t="n">
+      <c r="H55" s="2" t="n">
         <v>285</v>
       </c>
-      <c r="I55" t="n">
+      <c r="I55" s="2" t="n">
         <v>285</v>
       </c>
-      <c r="J55" t="n">
+      <c r="J55" s="2" t="n">
         <v>375</v>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="K55" s="2" t="inlineStr">
         <is>
           <t>WATER, SEPTIC,</t>
         </is>
@@ -3104,51 +3135,51 @@
       <c r="K56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>1633191</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>BUTLER'S BUS SERVICE INC</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>(802) 332-6171</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>1104 WEST WOODSTOCK ROAD</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>WOODSTOCK</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>VT</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>05091</t>
         </is>
       </c>
-      <c r="H57" t="n">
+      <c r="H57" s="2" t="n">
         <v>156</v>
       </c>
-      <c r="I57" t="n">
+      <c r="I57" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J57" t="n">
+      <c r="J57" s="2" t="n">
         <v>182</v>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3198,47 +3229,47 @@
       <c r="K58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>1985582</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>TITAN ELECTRIC INC</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr"/>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>5900 E YELLOWSTONE HWY</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>EVANSVILLE</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>WY</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>82636</t>
         </is>
       </c>
-      <c r="H59" t="n">
+      <c r="H59" s="2" t="n">
         <v>124</v>
       </c>
-      <c r="I59" t="n">
+      <c r="I59" s="2" t="n">
         <v>124</v>
       </c>
-      <c r="J59" t="n">
+      <c r="J59" s="2" t="n">
         <v>159</v>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="K59" s="2" t="inlineStr">
         <is>
           <t>ELECTRIC UTILITY TRUCK</t>
         </is>
@@ -3292,51 +3323,51 @@
       <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>2146883</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>TRK ENTERPRISES INC</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>(307) 631-0781</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>2020 CAREY AVE FLOOR 4</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>CHEYENNE</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>WY</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>82001</t>
         </is>
       </c>
-      <c r="H61" t="n">
+      <c r="H61" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="I61" t="n">
+      <c r="I61" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="J61" t="n">
+      <c r="J61" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3386,47 +3417,47 @@
       <c r="K62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>2347147</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>GLOBAL SPECIALIZED SERVICES LLC</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr"/>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>6360 E YELLOWSTONE HWY</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>EVANSVILLE</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>WY</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>82636</t>
         </is>
       </c>
-      <c r="H63" t="n">
+      <c r="H63" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="I63" t="n">
+      <c r="I63" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="J63" t="n">
+      <c r="J63" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3480,47 +3511,47 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>2575354</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>WALKER INSPECTION LLC</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr"/>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>1401 ECHETA ROAD</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>GILLETE</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>WY</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>82716</t>
         </is>
       </c>
-      <c r="H65" t="n">
+      <c r="H65" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="I65" t="n">
+      <c r="I65" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="J65" t="n">
+      <c r="J65" s="2" t="n">
         <v>62</v>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3570,51 +3601,51 @@
       <c r="K66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>3240911</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>ELEMENT TECHINCAL SERVICES LLC</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>(403) 930-0249</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>675 HERFORD LANE</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>CASPER</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>WY</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>82609</t>
         </is>
       </c>
-      <c r="H67" t="n">
+      <c r="H67" s="2" t="n">
         <v>68</v>
       </c>
-      <c r="I67" t="n">
+      <c r="I67" s="2" t="n">
         <v>68</v>
       </c>
-      <c r="J67" t="n">
+      <c r="J67" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3664,51 +3695,51 @@
       <c r="K68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>3423385</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>PARADISE EXPRESS INC</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>(888) 537-0558</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>4200 S POPLAR STREET SUITE 5</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>CASPER</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>WY</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>82601</t>
         </is>
       </c>
-      <c r="H69" t="n">
+      <c r="H69" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="I69" t="n">
+      <c r="I69" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="J69" t="n">
+      <c r="J69" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3754,51 +3785,51 @@
       <c r="K70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>4083116</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>CASELLA MID ATLANTIC LLC</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>(802) 772-2215</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>25 GREENS HILL LN</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>RUTLAND</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>VT</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>05701-3804</t>
         </is>
       </c>
-      <c r="H71" t="n">
+      <c r="H71" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="I71" t="n">
+      <c r="I71" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="J71" t="n">
+      <c r="J71" s="2" t="n">
         <v>106</v>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3852,47 +3883,47 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>4251471</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>VISIONARY COMMUNICATIONS LLC</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr"/>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>1001 S DOUGLAS HWY STE 201</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>GILLETTE</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>WY</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>82716-4957</t>
         </is>
       </c>
-      <c r="H73" t="n">
+      <c r="H73" s="2" t="n">
         <v>87</v>
       </c>
-      <c r="I73" t="n">
+      <c r="I73" s="2" t="n">
         <v>87</v>
       </c>
-      <c r="J73" t="n">
+      <c r="J73" s="2" t="n">
         <v>101</v>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3946,51 +3977,51 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>4498343</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>TM NATIONS LOGISTICS LLC</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>(307) 922-4705</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>295 GANNETT DR</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>ROCK SPRINGS</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>WY</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>82901</t>
         </is>
       </c>
-      <c r="H75" t="n">
+      <c r="H75" s="2" t="n">
         <v>67</v>
       </c>
-      <c r="I75" t="n">
+      <c r="I75" s="2" t="n">
         <v>67</v>
       </c>
-      <c r="J75" t="n">
+      <c r="J75" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4040,6 +4071,7 @@
       <c r="K76" t="inlineStr"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K76"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4052,14 +4084,18 @@
   </sheetPr>
   <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
